--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
@@ -6356,7 +6356,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
@@ -8326,7 +8326,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
@@ -8326,7 +8326,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
@@ -6356,7 +6356,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
@@ -6356,7 +6356,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
@@ -5662,7 +5662,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
@@ -5662,7 +5662,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
@@ -5662,7 +5662,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
@@ -5662,7 +5662,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
@@ -5662,7 +5662,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
@@ -5662,7 +5662,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
@@ -5662,7 +5662,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
@@ -5662,7 +5662,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
@@ -5662,7 +5662,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
@@ -5662,7 +5662,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
@@ -5662,7 +5662,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
@@ -6356,7 +6356,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
@@ -5662,7 +5662,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
@@ -5662,7 +5662,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
@@ -5662,7 +5662,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
@@ -6356,7 +6356,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
@@ -6356,7 +6356,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
@@ -5662,7 +5662,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260531_204920.xlsx
@@ -5662,7 +5662,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
